--- a/public/sampleFiles/service_donorSample_file.xlsx
+++ b/public/sampleFiles/service_donorSample_file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Thirdex\thirdxui\public\sampleFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC01A1-E231-4E1E-A7AA-0873FDB6AF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253F441A-A948-49DE-8832-0225E76B4731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <t>personalInfo_title</t>
   </si>
@@ -66,36 +66,6 @@
     <t>contactInfo_country</t>
   </si>
   <si>
-    <t>demo, deo</t>
-  </si>
-  <si>
-    <t>Engagement two, Engagement one</t>
-  </si>
-  <si>
-    <t>event two, event one</t>
-  </si>
-  <si>
-    <t>funding two</t>
-  </si>
-  <si>
-    <t>otherInfo_benificiary_information</t>
-  </si>
-  <si>
-    <t>otherInfo_campaigns_supported</t>
-  </si>
-  <si>
-    <t>otherInfo_engagement</t>
-  </si>
-  <si>
-    <t>otherInfo_events_attended</t>
-  </si>
-  <si>
-    <t>otherInfo_funding_interests</t>
-  </si>
-  <si>
-    <t>otherInfo_fundraising_activities</t>
-  </si>
-  <si>
     <t>otherInfo_file</t>
   </si>
   <si>
@@ -156,9 +126,6 @@
     <t>lorem dsrs ddff asad</t>
   </si>
   <si>
-    <t>demo, campaigns two</t>
-  </si>
-  <si>
     <t>three</t>
   </si>
   <si>
@@ -193,6 +160,12 @@
   </si>
   <si>
     <t>john, one</t>
+  </si>
+  <si>
+    <t>otherInfo_tags</t>
+  </si>
+  <si>
+    <t>emp1, Hindu</t>
   </si>
 </sst>
 </file>
@@ -514,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -531,17 +504,14 @@
     <col min="12" max="12" width="26.1796875" customWidth="1"/>
     <col min="13" max="13" width="16.1796875" customWidth="1"/>
     <col min="14" max="14" width="25.81640625" customWidth="1"/>
-    <col min="15" max="15" width="32.08984375" customWidth="1"/>
-    <col min="16" max="16" width="27.453125" customWidth="1"/>
-    <col min="18" max="18" width="42.54296875" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="23" max="30" width="20.6328125" customWidth="1"/>
-    <col min="31" max="31" width="25.26953125" customWidth="1"/>
-    <col min="32" max="32" width="19.26953125" customWidth="1"/>
-    <col min="33" max="33" width="15.90625" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="18" max="25" width="20.6328125" customWidth="1"/>
+    <col min="26" max="26" width="25.26953125" customWidth="1"/>
+    <col min="27" max="27" width="19.26953125" customWidth="1"/>
+    <col min="28" max="28" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -582,78 +552,63 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="U1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="D2" t="s">
         <v>25</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
       </c>
       <c r="E2" s="2">
         <v>37439</v>
@@ -665,96 +620,81 @@
         <v>9384840388</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L2">
         <v>88484</v>
       </c>
       <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2">
+        <v>45842</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="AA2" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="AB2" t="s">
         <v>42</v>
       </c>
-      <c r="V2" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" s="2">
-        <v>45842</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>53</v>
-      </c>
     </row>
-    <row r="3" spans="1:33" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2">
         <v>37440</v>
@@ -766,82 +706,67 @@
         <v>9384840388</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L3">
         <v>88485</v>
       </c>
       <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="2">
+        <v>45843</v>
+      </c>
+      <c r="T3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="1" t="s">
+      <c r="AA3" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="AB3" t="s">
         <v>42</v>
-      </c>
-      <c r="V3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W3" t="s">
-        <v>55</v>
-      </c>
-      <c r="X3" s="2">
-        <v>45843</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
